--- a/excel_templates/查看记录表.xlsx
+++ b/excel_templates/查看记录表.xlsx
@@ -458,363 +458,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bc95abf4-77c7-4182-adc3-e467905dc903</t>
+          <t>fc40cabe-67a1-4c91-b88e-cc26f315922f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ybb01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-10 16:54</t>
+          <t>2026-02-10 19:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7a8270ca-68e9-4b31-b5d0-4806038333e7</t>
+          <t>fef467d5-bcaf-44c4-95a6-338a305f2a7e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ybb01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-10 16:54</t>
+          <t>2026-02-10 19:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09d4bcbf-1b93-49fe-860c-19cfe93b7abc</t>
+          <t>2830d20c-4554-47dd-bb49-11e7bf52937b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>qt01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-10 16:55</t>
+          <t>2026-02-10 19:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9bf77a45-513c-498e-a68a-ff4d3061a79c</t>
+          <t>0f2666a3-f634-45a3-aeac-25e430b8a621</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>qt01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-10 16:55</t>
+          <t>2026-02-10 19:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>570d1829-351d-4d8a-8161-59914b49bf0c</t>
+          <t>89705dcd-48b6-4a03-b0eb-640477639fdb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>qwqe1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-10 16:56</t>
+          <t>2026-02-10 19:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d5e3bcd2-a56b-4116-b703-00a0d9a19eb3</t>
+          <t>d23b76f8-71d3-469f-9772-9bf2b67b6364</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>qwqe1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-10 16:56</t>
+          <t>2026-02-10 19:27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3aad21a1-18ef-482e-9895-07c22276b5b9</t>
+          <t>1ee9bd69-945f-4d70-88d3-d9daa0816115</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>qwqe1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-10 16:56</t>
+          <t>2026-02-10 19:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04ce0605-1a9d-4978-b556-695700b19348</t>
+          <t>a510385d-59a1-4dd8-a035-00d2c9889068</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-10 16:56</t>
+          <t>2026-02-10 19:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>859f4499-8326-44f9-b50c-e873c0d72d34</t>
+          <t>c48dd726-ec9b-4679-83aa-36c5d240023f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-10 16:56</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>878b7187-0035-42db-b94b-e82a12cdba28</t>
+          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ybb02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-10 16:57</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>403ca20e-fbea-4d37-a358-0161e5d1b80e</t>
+          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ybb02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-10 16:57</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c729912d-5de5-44bf-86c1-37fdfecc0b21</t>
+          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TEG-237</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-10 17:01</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2f0029fb-7a48-483d-bdf7-2cf95630c70c</t>
+          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TEG-237</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-10 17:01</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4b80563e-fdf9-49cb-865d-abacafd806fb</t>
+          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TEG-237</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,78 +824,78 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-10 17:06</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>397699f3-c531-4461-a14a-0dffbeeba02a</t>
+          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ybb02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-10 17:06</t>
+          <t>2026-02-10 19:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5888139e-b43f-42f2-8679-fa302c45f73d</t>
+          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TEG-237</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-10 17:06</t>
+          <t>2026-02-10 19:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6b8f9b9d-b642-45f0-9a54-860cb7c7a561</t>
+          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,24 +905,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-10 18:17</t>
+          <t>2026-02-10 19:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>673c7736-1ee5-4048-8db1-60e2401e4b0f</t>
+          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -937,19 +937,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-02-10 18:42</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>e46a88b5-75e8-42dd-a120-0fedde3abd0a</t>
+          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -964,19 +964,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-10 18:42</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>47d61daa-2d48-4b59-87f7-156b6a786e43</t>
+          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-10 18:43</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a3d10443-a24d-490c-8e52-402155555dc2</t>
+          <t>f97659ca-8913-478a-b734-573226791a9e</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1018,24 +1018,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-10 18:43</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>613a235a-eb0c-4525-919f-8cb5a69d9a4e</t>
+          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>qwqe3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,24 +1045,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-10 18:43</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>c2373ae4-9c92-4463-8a0b-7612890c404d</t>
+          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>qwqe3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,24 +1072,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-10 18:43</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cf63f666-4b88-4042-a63a-da3b1fdb11a8</t>
+          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-10 18:46</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>679eebf4-8aca-4c82-bb7e-4f5dc15a2735</t>
+          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-10 18:46</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9d7be35d-1f76-40eb-a4d7-fa0b39095170</t>
+          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>qt02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>其它设备</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-02-10 18:48</t>
+          <t>2026-02-10 19:48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>53531214-d90c-41df-9787-b2ee6b1ed79e</t>
+          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>qt02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>其它设备</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-10 18:49</t>
+          <t>2026-02-10 19:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1919858b-93e5-4c9e-96f8-41f75b9f6b63</t>
+          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,24 +1207,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-10 18:49</t>
+          <t>2026-02-10 19:49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fda0badc-cd55-487c-a94a-749222edabb7</t>
+          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,14 +1234,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-02-10 19:01</t>
+          <t>2026-02-10 19:49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fc40cabe-67a1-4c91-b88e-cc26f315922f</t>
+          <t>484615d7-1508-4b89-96d1-88436f139479</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1261,19 +1261,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-10 19:01</t>
+          <t>2026-02-10 19:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fef467d5-bcaf-44c4-95a6-338a305f2a7e</t>
+          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-10 19:08</t>
+          <t>2026-02-11 09:41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2830d20c-4554-47dd-bb49-11e7bf52937b</t>
+          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1315,19 +1315,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-02-10 19:13</t>
+          <t>2026-02-11 09:42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0f2666a3-f634-45a3-aeac-25e430b8a621</t>
+          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1342,19 +1342,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-02-10 19:18</t>
+          <t>2026-02-11 09:57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>89705dcd-48b6-4a03-b0eb-640477639fdb</t>
+          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,24 +1364,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-02-10 19:25</t>
+          <t>2026-02-11 10:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>d23b76f8-71d3-469f-9772-9bf2b67b6364</t>
+          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-10 19:27</t>
+          <t>2026-02-11 10:35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1ee9bd69-945f-4d70-88d3-d9daa0816115</t>
+          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,24 +1418,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-02-10 19:29</t>
+          <t>2026-02-11 10:57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>a510385d-59a1-4dd8-a035-00d2c9889068</t>
+          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1450,46 +1450,46 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-02-10 19:31</t>
+          <t>2026-02-11 12:52</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c48dd726-ec9b-4679-83aa-36c5d240023f</t>
+          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TEG-243</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 17:51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
+          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1504,19 +1504,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
+          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
+          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1558,19 +1558,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 19:33</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
+          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1585,24 +1585,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
+          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,19 +1612,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
+          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-10 19:39</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
+          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1666,19 +1666,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
+          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1693,73 +1693,73 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
+          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
+          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
+          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,24 +1769,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-11 19:40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>f97659ca-8913-478a-b734-573226791a9e</t>
+          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,240 +1796,240 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:42</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
+          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:43</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
+          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:44</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
+          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
+          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
+          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-11 20:17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
+          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-11 20:21</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
+          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-11 20:23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
+          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-11 20:24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>484615d7-1508-4b89-96d1-88436f139479</t>
+          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2039,24 +2039,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-10 19:57</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
+          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2066,24 +2066,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-11 09:41</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
+          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2093,24 +2093,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-11 09:42</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
+          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-02-11 09:57</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
+          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2152,19 +2152,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-02-11 10:34</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
+          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2179,24 +2179,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-11 10:35</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
+          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2206,46 +2206,46 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-11 10:57</t>
+          <t>2026-02-13 17:29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
+          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-11 12:52</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
+          <t>434fa301-0840-452a-93a6-226163a84f04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TEG-243</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2260,68 +2260,68 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-11 17:51</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
+          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
+          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-13 17:32</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
+          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2336,19 +2336,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-11 19:33</t>
+          <t>2026-02-13 17:38</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
+          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2363,51 +2363,51 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-13 17:50</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
+          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
+          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2417,83 +2417,83 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-24 10:37</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
+          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-24 11:29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
+          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-239</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-24 11:30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
+          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,24 +2503,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
+          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
+          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2557,14 +2557,14 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-11 19:40</t>
+          <t>2026-02-24 11:39</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
+          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-11 19:42</t>
+          <t>2026-02-24 11:40</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
+          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>ybb01</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机卡</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2611,338 +2611,338 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-11 19:43</t>
+          <t>2026-02-24 11:41</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
+          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-02-11 19:44</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
+          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
+          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-24 14:53</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
+          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-02-11 20:17</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
+          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-02-11 20:21</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
+          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-02-11 20:23</t>
+          <t>2026-02-24 15:01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
+          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-02-11 20:24</t>
+          <t>2026-02-24 15:02</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
+          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-24 15:08</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
+          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-24 16:38</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
+          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-24 16:41</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
+          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 16:42</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
+          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
+          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2957,56 +2957,56 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
+          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-02-13 17:29</t>
+          <t>2026-02-24 16:59</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
+          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 17:08</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>434fa301-0840-452a-93a6-226163a84f04</t>
+          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 17:13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
+          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,41 +3070,41 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 17:15</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
+          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-02-13 17:32</t>
+          <t>2026-02-24 17:16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
+          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3119,39 +3119,39 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-02-13 17:38</t>
+          <t>2026-02-24 17:20</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
+          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-02-13 17:50</t>
+          <t>2026-02-24 17:24</t>
         </is>
       </c>
     </row>

--- a/excel_templates/查看记录表.xlsx
+++ b/excel_templates/查看记录表.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fc40cabe-67a1-4c91-b88e-cc26f315922f</t>
+          <t>fef467d5-bcaf-44c4-95a6-338a305f2a7e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-10 19:01</t>
+          <t>2026-02-10 19:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fef467d5-bcaf-44c4-95a6-338a305f2a7e</t>
+          <t>2830d20c-4554-47dd-bb49-11e7bf52937b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-10 19:08</t>
+          <t>2026-02-10 19:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2830d20c-4554-47dd-bb49-11e7bf52937b</t>
+          <t>0f2666a3-f634-45a3-aeac-25e430b8a621</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -532,14 +532,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-10 19:13</t>
+          <t>2026-02-10 19:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0f2666a3-f634-45a3-aeac-25e430b8a621</t>
+          <t>89705dcd-48b6-4a03-b0eb-640477639fdb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -559,14 +559,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-10 19:18</t>
+          <t>2026-02-10 19:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>89705dcd-48b6-4a03-b0eb-640477639fdb</t>
+          <t>d23b76f8-71d3-469f-9772-9bf2b67b6364</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,14 +586,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-10 19:25</t>
+          <t>2026-02-10 19:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d23b76f8-71d3-469f-9772-9bf2b67b6364</t>
+          <t>1ee9bd69-945f-4d70-88d3-d9daa0816115</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,14 +613,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-10 19:27</t>
+          <t>2026-02-10 19:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1ee9bd69-945f-4d70-88d3-d9daa0816115</t>
+          <t>a510385d-59a1-4dd8-a035-00d2c9889068</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -640,19 +640,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-10 19:29</t>
+          <t>2026-02-10 19:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a510385d-59a1-4dd8-a035-00d2c9889068</t>
+          <t>c48dd726-ec9b-4679-83aa-36c5d240023f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,14 +667,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-10 19:31</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>c48dd726-ec9b-4679-83aa-36c5d240023f</t>
+          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
+          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
+          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
+          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -782,17 +782,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
+          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
+          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,14 +829,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
+          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -856,19 +856,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-10 19:39</t>
+          <t>2026-02-10 19:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
+          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
+          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -910,19 +910,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
+          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
+          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
+          <t>f97659ca-8913-478a-b734-573226791a9e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -991,24 +991,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f97659ca-8913-478a-b734-573226791a9e</t>
+          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>qwqe3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
+          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
+          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
+          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1106,17 +1106,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
+          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>qt02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>其它设备</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-10 19:48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
+          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1160,17 +1160,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
+          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-10 19:49</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
+          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1214,17 +1214,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
+          <t>484615d7-1508-4b89-96d1-88436f139479</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,19 +1234,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-10 19:57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>484615d7-1508-4b89-96d1-88436f139479</t>
+          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1261,14 +1261,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-10 19:57</t>
+          <t>2026-02-11 09:41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
+          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-11 09:41</t>
+          <t>2026-02-11 09:42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
+          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1315,19 +1315,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-02-11 09:42</t>
+          <t>2026-02-11 09:57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
+          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,24 +1337,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-02-11 09:57</t>
+          <t>2026-02-11 10:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
+          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1369,14 +1369,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-02-11 10:34</t>
+          <t>2026-02-11 10:35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
+          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1396,19 +1396,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-11 10:35</t>
+          <t>2026-02-11 10:57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
+          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,73 +1418,73 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-02-11 10:57</t>
+          <t>2026-02-11 12:52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
+          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>TEG-243</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-02-11 12:52</t>
+          <t>2026-02-11 17:51</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
+          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TEG-243</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-11 17:51</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
+          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
+          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-11 19:33</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
+          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-11 19:33</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
+          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
+          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
+          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1646,7 +1646,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
+          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1673,39 +1673,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
+          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
+          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
+          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1747,14 +1747,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-11 19:40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
+          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-11 19:40</t>
+          <t>2026-02-11 19:42</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
+          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1801,14 +1801,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-11 19:42</t>
+          <t>2026-02-11 19:43</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
+          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1828,14 +1828,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-11 19:43</t>
+          <t>2026-02-11 19:44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
+          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1855,19 +1855,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-02-11 19:44</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
+          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1889,12 +1889,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
+          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-11 20:17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
+          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1936,14 +1936,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-02-11 20:17</t>
+          <t>2026-02-11 20:21</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
+          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1963,19 +1963,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-02-11 20:21</t>
+          <t>2026-02-11 20:23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
+          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1990,19 +1990,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-02-11 20:23</t>
+          <t>2026-02-11 20:24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
+          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2017,19 +2017,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-02-11 20:24</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
+          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
+          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
+          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2078,12 +2078,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
+          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
+          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
+          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2159,17 +2159,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
+          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2179,14 +2179,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-13 17:29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
+          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-13 17:29</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
+          <t>434fa301-0840-452a-93a6-226163a84f04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2240,7 +2240,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>434fa301-0840-452a-93a6-226163a84f04</t>
+          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
+          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2287,24 +2287,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-13 17:32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
+          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2314,14 +2314,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-13 17:32</t>
+          <t>2026-02-13 17:38</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
+          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-13 17:38</t>
+          <t>2026-02-13 17:50</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
+          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2368,24 +2368,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-13 17:50</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
+          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,24 +2395,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-24 10:36</t>
+          <t>2026-02-24 10:37</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
+          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,19 +2422,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-24 10:37</t>
+          <t>2026-02-24 11:29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
+          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>TEG-239</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2449,24 +2449,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-24 11:29</t>
+          <t>2026-02-24 11:30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
+          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TEG-239</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2476,24 +2476,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-24 11:30</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
+          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2510,17 +2510,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
+          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-24 11:31</t>
+          <t>2026-02-24 11:39</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
+          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2557,24 +2557,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-24 11:39</t>
+          <t>2026-02-24 11:40</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
+          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>ybb01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机卡</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,41 +2584,41 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-24 11:40</t>
+          <t>2026-02-24 11:41</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
+          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ybb01</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-24 11:41</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
+          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
+          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2665,14 +2665,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-24 13:46</t>
+          <t>2026-02-24 14:53</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
+          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-24 14:53</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
+          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2726,7 +2726,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
+          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2746,14 +2746,14 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-02-24 15:00</t>
+          <t>2026-02-24 15:01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
+          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2773,14 +2773,14 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-02-24 15:01</t>
+          <t>2026-02-24 15:02</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
+          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2800,24 +2800,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-02-24 15:02</t>
+          <t>2026-02-24 15:08</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
+          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,14 +2827,14 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-02-24 15:08</t>
+          <t>2026-02-24 16:38</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
+          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-24 16:38</t>
+          <t>2026-02-24 16:41</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
+          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2881,19 +2881,19 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-24 16:41</t>
+          <t>2026-02-24 16:42</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
+          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2908,24 +2908,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-24 16:42</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
+          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
+          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2962,14 +2962,14 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-02-24 16:58</t>
+          <t>2026-02-24 16:59</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
+          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2984,19 +2984,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-02-24 16:59</t>
+          <t>2026-02-24 17:08</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
+          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-02-24 17:08</t>
+          <t>2026-02-24 17:13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
+          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3043,14 +3043,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-02-24 17:13</t>
+          <t>2026-02-24 17:15</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
+          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3065,19 +3065,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-02-24 17:15</t>
+          <t>2026-02-24 17:16</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
+          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-02-24 17:16</t>
+          <t>2026-02-24 17:20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
+          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,24 +3124,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-02-24 17:20</t>
+          <t>2026-02-24 17:24</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
+          <t>8a2e1ac4-302b-44f3-94c5-824119d5e285</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-02-24 17:24</t>
+          <t>2026-02-24 17:56</t>
         </is>
       </c>
     </row>

--- a/excel_templates/查看记录表.xlsx
+++ b/excel_templates/查看记录表.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fef467d5-bcaf-44c4-95a6-338a305f2a7e</t>
+          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-10 19:08</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2830d20c-4554-47dd-bb49-11e7bf52937b</t>
+          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,19 +505,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-10 19:13</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0f2666a3-f634-45a3-aeac-25e430b8a621</t>
+          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,19 +532,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-10 19:18</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>89705dcd-48b6-4a03-b0eb-640477639fdb</t>
+          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,24 +559,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-10 19:25</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d23b76f8-71d3-469f-9772-9bf2b67b6364</t>
+          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -586,19 +586,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-10 19:27</t>
+          <t>2026-02-10 19:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1ee9bd69-945f-4d70-88d3-d9daa0816115</t>
+          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,19 +613,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-10 19:29</t>
+          <t>2026-02-10 19:39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a510385d-59a1-4dd8-a035-00d2c9889068</t>
+          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,19 +640,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-10 19:31</t>
+          <t>2026-02-10 19:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>c48dd726-ec9b-4679-83aa-36c5d240023f</t>
+          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,19 +667,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
+          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -694,19 +694,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
+          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -721,19 +721,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
+          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,19 +748,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
+          <t>f97659ca-8913-478a-b734-573226791a9e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -775,24 +775,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
+          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>qwqe3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,24 +802,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
+          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>qwqe3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,24 +829,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-10 19:39</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
+          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,24 +856,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
+          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,24 +883,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-10 19:47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
+          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>qt02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>其它设备</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,24 +910,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-10 19:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
+          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>qt02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>其它设备</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,24 +937,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-10 19:48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
+          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -964,24 +964,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-10 19:49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f97659ca-8913-478a-b734-573226791a9e</t>
+          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -991,24 +991,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-10 19:49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
+          <t>484615d7-1508-4b89-96d1-88436f139479</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,24 +1018,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-10 19:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
+          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,24 +1045,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 09:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
+          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,24 +1072,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 09:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
+          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,105 +1099,105 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 09:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
+          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-11 10:34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
+          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-11 10:35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
+          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-11 10:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
+          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,46 +1207,46 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-11 12:52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>484615d7-1508-4b89-96d1-88436f139479</t>
+          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TEG-243</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-02-10 19:57</t>
+          <t>2026-02-11 17:51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
+          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1261,19 +1261,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-11 09:41</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
+          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-11 09:42</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
+          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1315,19 +1315,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-02-11 09:57</t>
+          <t>2026-02-11 19:33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
+          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,24 +1337,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-02-11 10:34</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
+          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,24 +1364,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-02-11 10:35</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
+          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-11 10:57</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
+          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1423,68 +1423,68 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-02-11 12:52</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
+          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TEG-243</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-02-11 17:51</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
+          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
+          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1494,24 +1494,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
+          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1526,19 +1526,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-11 19:33</t>
+          <t>2026-02-11 19:40</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
+          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1553,19 +1553,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-11 19:42</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
+          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1580,19 +1580,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-11 19:43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
+          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1607,19 +1607,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-11 19:44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
+          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1634,24 +1634,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
+          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,29 +1661,29 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
+          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,24 +1693,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-11 20:17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
+          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,19 +1720,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-11 20:21</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
+          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1747,14 +1747,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-11 19:40</t>
+          <t>2026-02-11 20:23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
+          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1774,19 +1774,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-11 19:42</t>
+          <t>2026-02-11 20:24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
+          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1801,19 +1801,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-11 19:43</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
+          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-11 19:44</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
+          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1855,19 +1855,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
+          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1882,19 +1882,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
+          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-11 20:17</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
+          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1936,24 +1936,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-02-11 20:21</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
+          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1963,24 +1963,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-02-11 20:23</t>
+          <t>2026-02-13 17:29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
+          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1990,24 +1990,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-02-11 20:24</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
+          <t>434fa301-0840-452a-93a6-226163a84f04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,24 +2017,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
+          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2044,24 +2044,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
+          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-13 17:32</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
+          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-13 17:38</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
+          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2125,24 +2125,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-13 17:50</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
+          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,24 +2152,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
+          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2179,19 +2179,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-13 17:29</t>
+          <t>2026-02-24 10:37</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
+          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2206,19 +2206,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 11:29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>434fa301-0840-452a-93a6-226163a84f04</t>
+          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>TEG-239</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2233,24 +2233,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 11:30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
+          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2260,19 +2260,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
+          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-13 17:32</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
+          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2314,14 +2314,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-13 17:38</t>
+          <t>2026-02-24 11:39</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
+          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-13 17:50</t>
+          <t>2026-02-24 11:40</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
+          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>ybb01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>手机卡</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2368,46 +2368,46 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-24 10:36</t>
+          <t>2026-02-24 11:41</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
+          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-24 10:37</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
+          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2417,24 +2417,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-24 11:29</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
+          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TEG-239</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2444,51 +2444,51 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-24 11:30</t>
+          <t>2026-02-24 14:53</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
+          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-24 11:31</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
+          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2498,110 +2498,110 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-24 11:31</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
+          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-24 11:39</t>
+          <t>2026-02-24 15:01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
+          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-24 11:40</t>
+          <t>2026-02-24 15:02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
+          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ybb01</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-24 11:41</t>
+          <t>2026-02-24 15:08</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
+          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2611,24 +2611,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-24 13:46</t>
+          <t>2026-02-24 16:38</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
+          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,24 +2638,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-02-24 13:46</t>
+          <t>2026-02-24 16:41</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
+          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,24 +2665,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-24 14:53</t>
+          <t>2026-02-24 16:42</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
+          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2692,24 +2692,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-24 15:00</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
+          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,24 +2719,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-02-24 15:00</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
+          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2746,105 +2746,105 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-02-24 15:01</t>
+          <t>2026-02-24 16:59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
+          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-02-24 15:02</t>
+          <t>2026-02-24 17:08</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
+          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-02-24 15:08</t>
+          <t>2026-02-24 17:13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
+          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-02-24 16:38</t>
+          <t>2026-02-24 17:15</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
+          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2854,24 +2854,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-24 16:41</t>
+          <t>2026-02-24 17:16</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
+          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,19 +2881,19 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-24 16:42</t>
+          <t>2026-02-24 17:20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
+          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2908,14 +2908,14 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-24 16:58</t>
+          <t>2026-02-24 17:24</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
+          <t>8a2e1ac4-302b-44f3-94c5-824119d5e285</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2935,24 +2935,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-02-24 16:58</t>
+          <t>2026-02-24 17:56</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
+          <t>0de02e08-88dd-4952-8745-d4a78fcfc30b</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2962,41 +2962,41 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-02-24 16:59</t>
+          <t>2026-02-25 09:28</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
+          <t>844b7f47-73ea-49b0-a5a9-2f12132bb461</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-02-24 17:08</t>
+          <t>2026-02-25 09:28</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
+          <t>60d56b21-fadf-4a22-89a7-97dd6b1746ed</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3011,19 +3011,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-02-24 17:13</t>
+          <t>2026-02-25 09:39</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
+          <t>55242623-2b0c-4834-bbb9-2a944c93d6ba</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3038,19 +3038,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-02-24 17:15</t>
+          <t>2026-02-25 09:40</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
+          <t>f930c02a-9ce8-49fb-a490-afba874c7936</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3070,14 +3070,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-02-24 17:16</t>
+          <t>2026-02-25 09:40</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
+          <t>145b3553-141b-430d-b902-f02744577e40</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-02-24 17:20</t>
+          <t>2026-02-25 09:40</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
+          <t>e866f264-0db5-47d0-bcac-39535117efb9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,14 +3124,14 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-02-24 17:24</t>
+          <t>2026-02-25 09:44</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8a2e1ac4-302b-44f3-94c5-824119d5e285</t>
+          <t>23cca678-844c-4666-9266-551b883bed20</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-02-24 17:56</t>
+          <t>2026-02-25 09:44</t>
         </is>
       </c>
     </row>

--- a/excel_templates/查看记录表.xlsx
+++ b/excel_templates/查看记录表.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ca4dd94d-cbf3-4f84-a765-d80ba33537ee</t>
+          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,19 +478,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 09:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>789c84cc-d2f4-4396-a095-d4d40118f81c</t>
+          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,19 +505,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 09:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>32cb48c7-8dd6-4f32-8f71-ff3e13876564</t>
+          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,14 +532,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 09:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2298ae70-7964-46e4-b7a3-78bfe4a77f02</t>
+          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,51 +554,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 10:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06bc03bc-f8d3-4b76-bbb3-a308b6b236db</t>
+          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-10 19:34</t>
+          <t>2026-02-11 10:35</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>67e8a2c3-7236-4d3f-893e-63715ae15761</t>
+          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,24 +608,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-10 19:39</t>
+          <t>2026-02-11 10:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6cad0cb4-ad18-4710-a0e0-817a6a61d856</t>
+          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,46 +640,46 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-11 12:52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dcc043c8-1297-4560-9938-681a9d6dd3d9</t>
+          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>TEG-243</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-10 19:41</t>
+          <t>2026-02-11 17:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cadde377-7238-4b3a-905a-fed3b61b20cf</t>
+          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -694,19 +694,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d9fa281b-470b-4a39-a62f-e80111642d65</t>
+          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -721,19 +721,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-11 19:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e6fa7ac7-bfed-4d00-81f4-e339adbf3a3b</t>
+          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,19 +748,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-10 19:43</t>
+          <t>2026-02-11 19:33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f97659ca-8913-478a-b734-573226791a9e</t>
+          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -775,24 +775,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a51869cc-5711-4071-b415-5283e4f26956</t>
+          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,24 +802,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>c6cb3f17-c8b6-4e67-9a39-e9820c848ee3</t>
+          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>qwqe3</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,24 +829,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>90eca4d8-cdf4-40f7-921d-81e0b2703580</t>
+          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,24 +856,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29f3da0b-2575-4441-b5e4-4f0ca59df2e0</t>
+          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,127 +883,127 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-10 19:47</t>
+          <t>2026-02-11 19:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2b53bbf7-8743-49f4-9bac-772d20209452</t>
+          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>54605a70-a0b5-4398-af28-0a5dd71ecef5</t>
+          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qt02</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>其它设备</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-02-10 19:48</t>
+          <t>2026-02-11 19:39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f686b616-3d8a-4739-b542-783fefecd1ed</t>
+          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-11 19:40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0141b966-f09f-4efb-b3bf-c52c09e912e9</t>
+          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TEG-199</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-10 19:49</t>
+          <t>2026-02-11 19:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>484615d7-1508-4b89-96d1-88436f139479</t>
+          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-10 19:57</t>
+          <t>2026-02-11 19:43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bbc7444a-da76-436f-98f1-b0c1e2a4c41d</t>
+          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,24 +1040,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-11 09:41</t>
+          <t>2026-02-11 19:44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9399f325-fb47-4285-89d7-0547e8e3f0ab</t>
+          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,24 +1067,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-11 09:42</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b7f3398d-6979-489f-a4b4-08f28507ccf5</t>
+          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,24 +1094,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-11 09:57</t>
+          <t>2026-02-11 20:16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2f899b9d-cf85-44dc-8018-01cf8f3f3b7a</t>
+          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-11 10:34</t>
+          <t>2026-02-11 20:17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5d8f7b5d-06c3-435e-b323-7cce99eed533</t>
+          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1153,19 +1153,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-02-11 10:35</t>
+          <t>2026-02-11 20:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>523349fe-f889-4763-af3a-e696b779c1d0</t>
+          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1180,19 +1180,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-11 10:57</t>
+          <t>2026-02-11 20:23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>337a86f5-2cd1-4c4f-8e35-1d5d42f85630</t>
+          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,29 +1202,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-11 12:52</t>
+          <t>2026-02-11 20:24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4f161042-bc1d-4f07-819e-b298ea3507f3</t>
+          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEG-243</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,19 +1234,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-02-11 17:51</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bbba2543-7802-431f-8bc1-9d304738f38d</t>
+          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>d46bf135-5d17-4682-b989-53b7928e1c34</t>
+          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,19 +1283,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-11 19:32</t>
+          <t>2026-02-11 20:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a24ac377-d762-4a1e-9bfe-ec6f7551eccf</t>
+          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1310,19 +1310,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-02-11 19:33</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dfed3dfc-9b84-45a1-9299-f5f16c9bf907</t>
+          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>e7b15476-541f-484b-9528-19d43c01b09e</t>
+          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1364,110 +1364,110 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-02-11 19:34</t>
+          <t>2026-02-13 17:27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1d036724-c1ce-4b6c-97d6-ec36db4b3f69</t>
+          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-13 17:29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0e65e2e6-9386-4765-b54a-08d2d4448908</t>
+          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6d9d2db1-3f91-4de0-9b49-8424f1ef25d7</t>
+          <t>434fa301-0840-452a-93a6-226163a84f04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-02-11 19:36</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>96f302d0-f873-4c0a-9cd0-59fbb822b41c</t>
+          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,24 +1477,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-13 17:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>544f712a-49f2-4c9a-8d09-330fdacc9f5e</t>
+          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,14 +1504,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-02-11 19:39</t>
+          <t>2026-02-13 17:32</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>859f9ae2-aac4-494b-a5bf-4c39bcccb45b</t>
+          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-11 19:40</t>
+          <t>2026-02-13 17:38</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>f3799417-1f5e-4230-aa58-06379cecf37c</t>
+          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1558,24 +1558,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-11 19:42</t>
+          <t>2026-02-13 17:50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a99c558b-e171-4fd6-a842-664526e3d498</t>
+          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,19 +1585,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-11 19:43</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1e8efa9d-8223-48e3-bdfc-72e701349409</t>
+          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1612,24 +1612,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-11 19:44</t>
+          <t>2026-02-24 10:37</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5ae1aa61-2864-4c1b-9c5f-e74e3792113b</t>
+          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-24 11:29</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>b27e8a90-48aa-4344-ac65-9a3c8647b974</t>
+          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>066032d8-0a4f-4d29-9e68-3495859bd8ef</t>
+          <t>TEG-239</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,19 +1666,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-11 20:16</t>
+          <t>2026-02-24 11:30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6b50f51e-48c0-40e0-b27f-300d06fc5daf</t>
+          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1693,24 +1693,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-11 20:17</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>d535bd4c-3a1d-43d3-b584-52adfb2e09b3</t>
+          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>PHO001</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,19 +1720,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-11 20:21</t>
+          <t>2026-02-24 11:31</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8d2fde4c-972c-4879-aba3-06be32233b4a</t>
+          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1747,14 +1747,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-11 20:23</t>
+          <t>2026-02-24 11:39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8e191e09-4622-42d5-9248-459d07b3ccf4</t>
+          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1774,24 +1774,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-11 20:24</t>
+          <t>2026-02-24 11:40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b14cb403-2a37-4660-9370-fe7c6fa1a774</t>
+          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>ybb01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机卡</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1801,154 +1801,154 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-24 11:41</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>877a9c17-a5ca-48eb-b683-c8307fe74c7a</t>
+          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>59aed345-d8f2-41a3-8395-4121ac52f33c</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>82342cc5-16ae-4c00-bec2-3ac957733110</t>
+          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>066bcbbf-d6cf-4e83-a705-f6c0052f70db</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-02-11 20:30</t>
+          <t>2026-02-24 13:46</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>72417d38-1d02-4284-abf7-79a166c82239</t>
+          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 14:53</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>e19dd98c-a10d-4b8b-8e32-79bcb1eda16c</t>
+          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>94a63142-6dec-4bee-91ed-6a2b408e0d30</t>
+          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-02-13 17:27</t>
+          <t>2026-02-24 15:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>b0789d99-72ae-4747-9152-7b6adb22d88e</t>
+          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-02-13 17:29</t>
+          <t>2026-02-24 15:01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>98fbc452-ed35-4c39-a9bb-7e5ecbfee583</t>
+          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1985,24 +1985,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 15:02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>434fa301-0840-452a-93a6-226163a84f04</t>
+          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2012,159 +2012,159 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 15:08</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>456dddc8-85d2-42e1-bbb8-dd128bb14309</t>
+          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-13 17:30</t>
+          <t>2026-02-24 16:38</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7b2176cb-a22f-4f18-a221-288debbc9579</t>
+          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TEG-238</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-13 17:32</t>
+          <t>2026-02-24 16:41</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6563684a-1d73-44e0-80de-bede399dae14</t>
+          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-13 17:38</t>
+          <t>2026-02-24 16:42</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22f9b377-5d3c-4032-bbca-6f278b24bb10</t>
+          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-02-13 17:50</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>34d63a7f-2324-4f31-aa10-1884f0e2a885</t>
+          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-02-24 10:36</t>
+          <t>2026-02-24 16:58</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0e18045e-5b18-467e-887e-e547f310c5e0</t>
+          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>f8770a88-1a0d-47c3-a478-f8a7a02688d9</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2174,29 +2174,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-24 10:37</t>
+          <t>2026-02-24 16:59</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>73ed1091-1117-4770-bd0c-53e2c560c920</t>
+          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2206,24 +2206,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-24 11:29</t>
+          <t>2026-02-24 17:08</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0a9a84e4-dc29-4e5e-8d08-088b2e3e0def</t>
+          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TEG-239</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2233,14 +2233,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-24 11:30</t>
+          <t>2026-02-24 17:13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>126ad803-01a8-4f61-a843-2520119efd8e</t>
+          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2260,41 +2260,41 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-24 11:31</t>
+          <t>2026-02-24 17:15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>39ff80cf-b62e-4b56-9bb1-5b529acfc251</t>
+          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PHO001</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-24 11:31</t>
+          <t>2026-02-24 17:16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>71456988-4289-4505-bc30-186c1e52fa7c</t>
+          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2309,73 +2309,73 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-24 11:39</t>
+          <t>2026-02-24 17:20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>62972475-d0c4-49e2-a3b4-e6441d55d83c</t>
+          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-24 11:40</t>
+          <t>2026-02-24 17:24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>b266c543-434c-40f4-adbd-018ec463dd10</t>
+          <t>8a2e1ac4-302b-44f3-94c5-824119d5e285</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ybb01</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>手机卡</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-24 11:41</t>
+          <t>2026-02-24 17:56</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ddba7f92-6ac2-4af6-8ff7-04921b0c4652</t>
+          <t>0de02e08-88dd-4952-8745-d4a78fcfc30b</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2395,14 +2395,14 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-24 13:46</t>
+          <t>2026-02-25 09:28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1888aa55-8047-48cc-a3e3-8dded11865c2</t>
+          <t>844b7f47-73ea-49b0-a5a9-2f12132bb461</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2422,24 +2422,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-24 13:46</t>
+          <t>2026-02-25 09:28</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>feb8f32c-b22b-4abc-a586-04e4f942e989</t>
+          <t>60d56b21-fadf-4a22-89a7-97dd6b1746ed</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,24 +2449,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-24 14:53</t>
+          <t>2026-02-25 09:39</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>482bec26-6d8e-4d0d-900a-da30c5f6f894</t>
+          <t>55242623-2b0c-4834-bbb9-2a944c93d6ba</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2476,24 +2476,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-24 15:00</t>
+          <t>2026-02-25 09:40</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9b488d95-0453-4445-9479-7a6b8bc2a1cc</t>
+          <t>f930c02a-9ce8-49fb-a490-afba874c7936</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,24 +2503,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-24 15:00</t>
+          <t>2026-02-25 09:40</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>f7649e6f-922b-49e2-978d-f0ef1c23e681</t>
+          <t>145b3553-141b-430d-b902-f02744577e40</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,24 +2530,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-24 15:01</t>
+          <t>2026-02-25 09:40</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6a8dd01e-0801-4e05-8952-9fa3786be5db</t>
+          <t>e866f264-0db5-47d0-bcac-39535117efb9</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,24 +2557,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-24 15:02</t>
+          <t>2026-02-25 09:44</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0a95efb2-230d-4629-835e-bf7fa84710cb</t>
+          <t>23cca678-844c-4666-9266-551b883bed20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-24 15:08</t>
+          <t>2026-02-25 09:44</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>f9ca9ca3-e9a3-4ee6-a069-303e4725c6a6</t>
+          <t>93aa4a0d-7d95-4b6b-92b3-4b15b7da5dac</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2611,24 +2611,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-24 16:38</t>
+          <t>2026-02-25 10:02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dfc76377-be3f-4907-8734-ca726187296d</t>
+          <t>f8612c89-1760-4f5a-abe9-8b42a00e900c</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>车机</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,24 +2638,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-02-24 16:41</t>
+          <t>2026-02-25 10:05</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5746dcfa-0727-40e7-a59b-2f3e765b0609</t>
+          <t>9f10b050-48af-43c9-b3ac-21168da97ba7</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>qwqe4</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,24 +2665,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-24 16:42</t>
+          <t>2026-02-25 10:24</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>f14f256f-0740-4645-a423-ed28c4ad6b42</t>
+          <t>5af90154-27ea-41ee-b44c-1361ee26e98b</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>qwqe2</t>
+          <t>TEG-199</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2692,186 +2692,186 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-24 16:58</t>
+          <t>2026-02-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>408fd05d-b854-4c69-838c-67f79bcc7e9d</t>
+          <t>f9801153-5f3d-4798-8992-a995d909903a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-02-24 16:58</t>
+          <t>2026-02-25 10:33</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>cbf245be-32b4-48c6-984e-fbf75c280ee9</t>
+          <t>1c512824-b973-4b15-8bf3-39ee96011596</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-02-24 16:59</t>
+          <t>2026-02-25 10:33</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>919bc52d-2769-4f79-a36b-6c6df96e817c</t>
+          <t>896eea77-ca81-423b-88a5-5838ba82040f</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-02-24 17:08</t>
+          <t>2026-02-25 11:01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>71bf2471-d8b9-4a2a-a697-052a404a795b</t>
+          <t>45656e33-4c49-4d33-bfc3-7bc4698aa699</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-02-24 17:13</t>
+          <t>2026-02-25 11:06</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4fe27813-e000-48fa-b6d5-287f45460df8</t>
+          <t>f4f85fbc-24b5-4683-bb2a-f60af7cbc072</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-02-24 17:15</t>
+          <t>2026-02-25 11:15</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2003118f-0e10-48c6-a8c3-8540fa316580</t>
+          <t>ca324084-bfba-4caa-ba45-62839de4e186</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-24 17:16</t>
+          <t>2026-02-25 11:17</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>fbde71bc-999f-4193-8809-1434a070fdbb</t>
+          <t>364eb412-3238-4db3-b56c-a87701483b13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,14 +2881,14 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-24 17:20</t>
+          <t>2026-02-25 11:19</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>908a7a78-a2e7-44cb-b498-117a7825228c</t>
+          <t>6e6b7504-5802-451b-a14d-f63110ec3a00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2908,24 +2908,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-24 17:24</t>
+          <t>2026-02-25 11:20</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8a2e1ac4-302b-44f3-94c5-824119d5e285</t>
+          <t>2f405027-ddd1-4b4f-a88b-e205e22dcbc3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2935,132 +2935,132 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-02-24 17:56</t>
+          <t>2026-02-25 11:21</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0de02e08-88dd-4952-8745-d4a78fcfc30b</t>
+          <t>0032bf6e-6ede-41b8-b8f0-7a6266d3fe68</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-02-25 09:28</t>
+          <t>2026-02-25 11:25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>844b7f47-73ea-49b0-a5a9-2f12132bb461</t>
+          <t>f388acc9-8cd8-4b59-9681-89bd3a2f2f4a</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-02-25 09:28</t>
+          <t>2026-02-25 11:27</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>60d56b21-fadf-4a22-89a7-97dd6b1746ed</t>
+          <t>0ee890f2-4acf-4252-bb23-8aaa2d97634d</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-02-25 09:39</t>
+          <t>2026-02-25 11:27</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>55242623-2b0c-4834-bbb9-2a944c93d6ba</t>
+          <t>c1dda869-2089-45c0-b67a-d707a814cd06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-02-25 09:40</t>
+          <t>2026-02-25 11:28</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>f930c02a-9ce8-49fb-a490-afba874c7936</t>
+          <t>77288d3d-27eb-48a2-8aef-a472ee8d5b32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>qwqe4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>仪表</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,24 +3070,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-02-25 09:40</t>
+          <t>2026-02-25 11:33</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>145b3553-141b-430d-b902-f02744577e40</t>
+          <t>abcc5fbc-d05c-4ba7-bcd4-7a4ac17bdb54</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>TEG-238</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-02-25 09:40</t>
+          <t>2026-02-25 11:36</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>e866f264-0db5-47d0-bcac-39535117efb9</t>
+          <t>93912f64-9d80-4f96-8ddb-44495a07fa0e</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,24 +3124,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-02-25 09:44</t>
+          <t>2026-02-25 11:37</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>23cca678-844c-4666-9266-551b883bed20</t>
+          <t>3ae6f522-7b80-45a7-a950-c78297d371d9</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>车机</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-02-25 09:44</t>
+          <t>2026-02-25 11:37</t>
         </is>
       </c>
     </row>
